--- a/Task-2-Bug-Report-by(sanjay srinivas T).xlsx
+++ b/Task-2-Bug-Report-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1158FF1D-4408-4665-8887-1EADBFB1C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{1158FF1D-4408-4665-8887-1EADBFB1C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A75606C-4275-41AC-BF51-74F5F072E1D2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D1B541F-7919-4ACF-887F-75DE45B65CCD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
   <si>
     <t>BUG REPORT</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>special characters are blocked immediately. No validation message is displayed</t>
+  </si>
+  <si>
+    <t>TESTED BY:SANJAY SRINIVAS T</t>
   </si>
 </sst>
 </file>
@@ -284,7 +287,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,6 +359,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="14">
     <border>
@@ -513,7 +522,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -521,8 +530,9 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -606,8 +616,44 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -624,52 +670,20 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
+  <cellStyles count="8">
     <cellStyle name="20% - Accent4" xfId="2" builtinId="42"/>
     <cellStyle name="40% - Accent5" xfId="4" builtinId="47"/>
+    <cellStyle name="60% - Accent2" xfId="7" builtinId="36"/>
     <cellStyle name="60% - Accent4" xfId="3" builtinId="44"/>
     <cellStyle name="60% - Accent6" xfId="5" builtinId="52"/>
     <cellStyle name="Accent1" xfId="1" builtinId="29"/>
@@ -1000,116 +1014,118 @@
     <col min="9" max="9" width="20.453125" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.26953125" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.453125" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="1"/>
+    <col min="12" max="12" width="8.7265625" style="1"/>
+    <col min="13" max="13" width="12.90625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E1" s="47" t="s">
+      <c r="E1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="43"/>
+      <c r="B2" s="30"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="44" t="s">
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="43"/>
-      <c r="C3" s="48" t="s">
+      <c r="B3" s="30"/>
+      <c r="C3" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="G3" s="43" t="s">
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="G3" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="44" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="44"/>
-      <c r="L3" s="44"/>
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44" t="s">
+      <c r="B4" s="30"/>
+      <c r="C4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="G4" s="43" t="s">
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="G4" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="45">
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="35">
         <v>46029</v>
       </c>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="46"/>
-      <c r="C5" s="44" t="s">
+      <c r="B5" s="36"/>
+      <c r="C5" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="G5" s="46" t="s">
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="G5" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="45">
-        <v>46088</v>
-      </c>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="35">
+        <v>46060</v>
+      </c>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="37"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
+      <c r="E8" s="37"/>
+      <c r="F8" s="37"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -1125,10 +1141,10 @@
       <c r="D9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="36"/>
+      <c r="F9" s="39"/>
       <c r="G9" s="4" t="s">
         <v>19</v>
       </c>
@@ -1154,10 +1170,10 @@
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="39"/>
+      <c r="F10" s="40"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -1171,8 +1187,8 @@
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -1194,10 +1210,10 @@
       <c r="D12" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="41" t="s">
+      <c r="E12" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="42"/>
+      <c r="F12" s="34"/>
       <c r="G12" s="12" t="s">
         <v>31</v>
       </c>
@@ -1223,8 +1239,8 @@
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="32"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="17"/>
       <c r="H13" s="17"/>
       <c r="I13" s="17"/>
@@ -1253,10 +1269,10 @@
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
-      <c r="E15" s="33" t="s">
+      <c r="E15" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="34"/>
+      <c r="F15" s="46"/>
       <c r="G15" s="17"/>
       <c r="H15" s="18"/>
       <c r="M15" s="2"/>
@@ -1274,10 +1290,10 @@
       <c r="D16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="36"/>
+      <c r="F16" s="39"/>
       <c r="G16" s="4" t="s">
         <v>40</v>
       </c>
@@ -1303,10 +1319,10 @@
       <c r="D17" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="47" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="37"/>
+      <c r="F17" s="47"/>
       <c r="G17" s="25" t="s">
         <v>47</v>
       </c>
@@ -1328,10 +1344,10 @@
       <c r="D18" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="37"/>
+      <c r="F18" s="47"/>
       <c r="G18" s="25" t="s">
         <v>52</v>
       </c>
@@ -1345,24 +1361,28 @@
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="M20" s="2"/>
+      <c r="E20" s="37"/>
+      <c r="F20" s="37"/>
+      <c r="I20" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="49"/>
+      <c r="K20" s="49"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="27"/>
       <c r="B21" s="27"/>
       <c r="C21" s="27"/>
       <c r="D21" s="27"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
       <c r="G21" s="27"/>
       <c r="H21" s="27"/>
       <c r="I21" s="27"/>
@@ -1372,23 +1392,26 @@
       <c r="M21" s="28"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
+      <c r="E22" s="37"/>
+      <c r="F22" s="37"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
+      <c r="E23" s="37"/>
+      <c r="F23" s="37"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
+  <mergeCells count="33">
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
@@ -1403,16 +1426,14 @@
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{A8D390F2-6B07-4EFD-A705-61078C4CD09A}"/>

--- a/Task-2-Bug-Report-by(sanjay srinivas T).xlsx
+++ b/Task-2-Bug-Report-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{1158FF1D-4408-4665-8887-1EADBFB1C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A75606C-4275-41AC-BF51-74F5F072E1D2}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{1158FF1D-4408-4665-8887-1EADBFB1C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E004DA12-8FEA-495B-87AD-702397DA300F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D1B541F-7919-4ACF-887F-75DE45B65CCD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
   <si>
     <t>BUG REPORT</t>
   </si>
@@ -48,9 +48,6 @@
     <t>TEST DESIGNED BY:</t>
   </si>
   <si>
-    <t>SANJAY SRINIVAS</t>
-  </si>
-  <si>
     <t>APPLICATION URL:</t>
   </si>
   <si>
@@ -63,9 +60,6 @@
     <t>ENVIRONMENT:</t>
   </si>
   <si>
-    <t>WINDOWS 10/CHROME 138</t>
-  </si>
-  <si>
     <t>TESTING STARTED DATE:</t>
   </si>
   <si>
@@ -112,9 +106,6 @@
   </si>
   <si>
     <t>BUG</t>
-  </si>
-  <si>
-    <t>bug-001</t>
   </si>
   <si>
     <t>Login</t>
@@ -198,9 +189,6 @@
     <t>The field should accept only alphabetic characters</t>
   </si>
   <si>
-    <t>special characters are blocked immediately. No validation message is displayed.</t>
-  </si>
-  <si>
     <t>OBS-002</t>
   </si>
   <si>
@@ -213,10 +201,49 @@
     <t>The field should accept only alphabetic characters.</t>
   </si>
   <si>
-    <t>special characters are blocked immediately. No validation message is displayed</t>
-  </si>
-  <si>
-    <t>TESTED BY:SANJAY SRINIVAS T</t>
+    <t>BUG_ID-001</t>
+  </si>
+  <si>
+    <t>BUG_ID-002</t>
+  </si>
+  <si>
+    <t>google sign in account cannot authenticate in email addess field</t>
+  </si>
+  <si>
+    <t>account created using google sign in</t>
+  </si>
+  <si>
+    <t>open application,click sign in,enter the same gmail id which is used in continue with google</t>
+  </si>
+  <si>
+    <t>enter google id which is used in continue with google</t>
+  </si>
+  <si>
+    <t>application should recognize the account was created using continue with google authentication so (1)redirect to the  google sign in page (2)display message "continue with google or set password using forgot password"</t>
+  </si>
+  <si>
+    <t>password page is displayed even the password was not created during sign in</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>REPORTED BY:SANJAY SRINIVAS T</t>
+  </si>
+  <si>
+    <t>SANJAY SRINIVAS T</t>
+  </si>
+  <si>
+    <t>WINDOWS 10/CHROME 138/ MicroSoft Edge</t>
+  </si>
+  <si>
+    <t>special characters are blocked immediately. But no validation message is displayed.</t>
+  </si>
+  <si>
+    <t>special characters are blocked immediately. But no validation message is displayed</t>
   </si>
 </sst>
 </file>
@@ -366,7 +393,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -519,6 +546,19 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -532,7 +572,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -571,12 +611,6 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -616,67 +650,91 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1000,7 +1058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824908B9-BB61-4910-8A5E-B394F0F024BC}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" style="1" customWidth="1"/>
@@ -1009,7 +1067,7 @@
     <col min="4" max="4" width="20.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.36328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.6328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.6328125" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.453125" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.26953125" style="1" customWidth="1"/>
@@ -1020,148 +1078,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E1" s="29" t="s">
+      <c r="E1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="30"/>
+      <c r="B2" s="39"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="31" t="s">
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A3" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="31"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="30" t="s">
+      <c r="B3" s="39"/>
+      <c r="C3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="32" t="s">
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="G3" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="G3" s="30" t="s">
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="2"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A4" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="31" t="s">
-        <v>4</v>
-      </c>
-      <c r="K3" s="31"/>
-      <c r="L3" s="31"/>
-      <c r="M3" s="2"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="30" t="s">
+      <c r="B4" s="39"/>
+      <c r="C4" s="40" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="G4" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31" t="s">
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="41">
+        <v>46029</v>
+      </c>
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="2"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A5" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="G4" s="30" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="35">
-        <v>46029</v>
-      </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="36" t="s">
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="G5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="G5" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="35">
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="41">
         <v>46060</v>
       </c>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
+      <c r="K5" s="40"/>
+      <c r="L5" s="40"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="37"/>
-      <c r="B6" s="37"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="E9" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="F9" s="35"/>
+      <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="H9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="39"/>
-      <c r="G9" s="4" t="s">
+      <c r="I9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="J9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="K9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="L9" s="4" t="s">
         <v>22</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="M9" s="5"/>
     </row>
@@ -1170,10 +1228,10 @@
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="40"/>
+      <c r="E10" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="43"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -1187,8 +1245,8 @@
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -1199,233 +1257,246 @@
     </row>
     <row r="12" spans="1:13" ht="223.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="E12" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="F12" s="38"/>
+      <c r="G12" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="H12" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="I12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="12" t="s">
+      <c r="J12" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="K12" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="L12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="L12" s="16" t="s">
-        <v>35</v>
-      </c>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="43"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
+    <row r="13" spans="1:13" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="38"/>
+      <c r="G13" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="14" t="s">
+        <v>57</v>
+      </c>
       <c r="M13" s="5"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="21"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="30"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
       <c r="M14" s="5"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="45" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="19"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="33"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16"/>
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="46"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="18"/>
-      <c r="M15" s="2"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16" s="4" t="s">
+      <c r="F17" s="35"/>
+      <c r="G17" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="H17" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="38" t="s">
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" spans="1:13" ht="166.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="39"/>
-      <c r="G16" s="4" t="s">
+      <c r="B18" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="C18" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" ht="166.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="23" t="s">
+      <c r="D18" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="E18" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="F18" s="36"/>
+      <c r="G18" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" ht="194" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="24" t="s">
+      <c r="B19" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="E17" s="47" t="s">
+      <c r="D19" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="F17" s="47"/>
-      <c r="G17" s="25" t="s">
+      <c r="E19" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" ht="194" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="47" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="47"/>
-      <c r="G18" s="25" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="53" t="s">
+        <v>33</v>
+      </c>
       <c r="M19" s="2"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="I20" s="49" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="49"/>
-      <c r="K20" s="49"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="54"/>
+      <c r="M20" s="2"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="I21" s="27" t="s">
+        <v>58</v>
+      </c>
       <c r="J21" s="27"/>
       <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="28"/>
+      <c r="M21" s="2"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="26"/>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
-    <mergeCell ref="I20:K20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
+  <mergeCells count="34">
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="G2:I2"/>
@@ -1434,6 +1505,32 @@
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="J3:L3"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{A8D390F2-6B07-4EFD-A705-61078C4CD09A}"/>

--- a/Task-2-Bug-Report-by(sanjay srinivas T).xlsx
+++ b/Task-2-Bug-Report-by(sanjay srinivas T).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3fc2e1139c06ea87/Desktop/Tichi-assignment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{1158FF1D-4408-4665-8887-1EADBFB1C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E004DA12-8FEA-495B-87AD-702397DA300F}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{1158FF1D-4408-4665-8887-1EADBFB1C5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C1F580F-51B6-44A4-873E-365FE5A446FC}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9D1B541F-7919-4ACF-887F-75DE45B65CCD}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="78">
   <si>
     <t>BUG REPORT</t>
   </si>
@@ -244,6 +244,51 @@
   </si>
   <si>
     <t>special characters are blocked immediately. But no validation message is displayed</t>
+  </si>
+  <si>
+    <t>BUG_ID_003</t>
+  </si>
+  <si>
+    <t>Login Email Address field accepts input exceeding maximum allowed length without validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">user in login page </t>
+  </si>
+  <si>
+    <t>(1).open login page,(2).enter email address with more length(254 characters).(3)click continue</t>
+  </si>
+  <si>
+    <t>aaaaaaaaaaaaaaaaaaaaaaaaaaaa(254+)@gmail.com</t>
+  </si>
+  <si>
+    <t>The application should restrict the input length or display an appropriate validation message. And remain the user in the login page.</t>
+  </si>
+  <si>
+    <t>The application accepts excessively long email input without any message and allowing user to next page.</t>
+  </si>
+  <si>
+    <t>BUG_ID_004</t>
+  </si>
+  <si>
+    <t>Signup</t>
+  </si>
+  <si>
+    <t>First Name and Last Name fields accept excessive character input without maximum length validation</t>
+  </si>
+  <si>
+    <t>user is in login page</t>
+  </si>
+  <si>
+    <t>(1).open login page,(2).enter more length of character in both first and last name field.(3)observe the field behavior.(4)click signup</t>
+  </si>
+  <si>
+    <t>aaaaaaaaaaaaa(100+) and bbbbbbbbb(100+)</t>
+  </si>
+  <si>
+    <t>The application should restrict the input to the maximum allowed length or display a validation message indicating the allowed character limit and not permit the user to signup</t>
+  </si>
+  <si>
+    <t>The application accepts excessively long input without restricting the length or displaying any validation message</t>
   </si>
 </sst>
 </file>
@@ -650,14 +695,68 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -671,70 +770,16 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="6" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,7 +1103,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{824908B9-BB61-4910-8A5E-B394F0F024BC}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="19.26953125" style="1" customWidth="1"/>
@@ -1067,7 +1112,7 @@
     <col min="4" max="4" width="20.6328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.1796875" style="1" customWidth="1"/>
     <col min="6" max="6" width="16.36328125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="22.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.6328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.6328125" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.453125" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.26953125" style="1" customWidth="1"/>
@@ -1078,112 +1123,112 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E1" s="45" t="s">
+      <c r="E1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
+      <c r="B2" s="35"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="G2" s="39" t="s">
+      <c r="G2" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="40" t="s">
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
+      <c r="K2" s="36"/>
+      <c r="L2" s="36"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="46" t="s">
+      <c r="B3" s="35"/>
+      <c r="C3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="G3" s="39" t="s">
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="G3" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40" t="s">
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
       <c r="M3" s="2"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="39" t="s">
+      <c r="A4" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="G4" s="39" t="s">
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="G4" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="41">
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="38">
         <v>46029</v>
       </c>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="36"/>
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="40" t="s">
+      <c r="B5" s="39"/>
+      <c r="C5" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="G5" s="42" t="s">
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="G5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="41">
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="38">
         <v>46060</v>
       </c>
-      <c r="K5" s="40"/>
-      <c r="L5" s="40"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
       <c r="M5" s="2"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
       <c r="M6" s="2"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="M7" s="2"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
       <c r="M8" s="2"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -1199,10 +1244,10 @@
       <c r="D9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="35"/>
+      <c r="F9" s="45"/>
       <c r="G9" s="4" t="s">
         <v>17</v>
       </c>
@@ -1228,10 +1273,10 @@
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="43"/>
+      <c r="F10" s="46"/>
       <c r="G10" s="6"/>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
@@ -1245,8 +1290,8 @@
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
       <c r="G11" s="8"/>
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
@@ -1268,10 +1313,10 @@
       <c r="D12" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="38"/>
+      <c r="F12" s="42"/>
       <c r="G12" s="12" t="s">
         <v>28</v>
       </c>
@@ -1281,10 +1326,10 @@
       <c r="I12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="J12" s="47" t="s">
+      <c r="J12" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="K12" s="48" t="s">
+      <c r="K12" s="28" t="s">
         <v>31</v>
       </c>
       <c r="L12" s="14" t="s">
@@ -1305,10 +1350,10 @@
       <c r="D13" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="38"/>
+      <c r="F13" s="42"/>
       <c r="G13" s="12" t="s">
         <v>53</v>
       </c>
@@ -1318,10 +1363,10 @@
       <c r="I13" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="47" t="s">
+      <c r="J13" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="48" t="s">
+      <c r="K13" s="28" t="s">
         <v>56</v>
       </c>
       <c r="L13" s="14" t="s">
@@ -1329,34 +1374,78 @@
       </c>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="15"/>
+    <row r="14" spans="1:13" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="42"/>
+      <c r="G14" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="14" t="s">
+        <v>32</v>
+      </c>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" s="17"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="19"/>
+    <row r="15" spans="1:13" ht="304.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" s="42"/>
+      <c r="G15" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J15" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="14" t="s">
+        <v>32</v>
+      </c>
       <c r="M15" s="5"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
@@ -1364,153 +1453,177 @@
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="48"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A17" s="17"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="19"/>
+      <c r="M17" s="5"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="33"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="16"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A17" s="4" t="s">
+      <c r="F18" s="51"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16"/>
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E19" s="44" t="s">
         <v>36</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="4" t="s">
+      <c r="F19" s="45"/>
+      <c r="G19" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H19" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="I17"/>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" spans="1:13" ht="166.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="21" t="s">
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" spans="1:13" ht="166.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B20" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C20" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D20" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="36" t="s">
+      <c r="E20" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="36"/>
-      <c r="G18" s="23" t="s">
+      <c r="F20" s="52"/>
+      <c r="G20" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="24" t="s">
+      <c r="H20" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="M18" s="2"/>
-    </row>
-    <row r="19" spans="1:13" ht="194" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="49" t="s">
+      <c r="M20" s="2"/>
+    </row>
+    <row r="21" spans="1:13" ht="194" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="B19" s="49" t="s">
+      <c r="B21" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="50" t="s">
+      <c r="C21" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="50" t="s">
+      <c r="D21" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="51" t="s">
+      <c r="E21" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="51"/>
-      <c r="G19" s="52" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="53" t="s">
+      <c r="H21" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="M19" s="2"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A20" s="54"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="55"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="54"/>
-      <c r="M20" s="2"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="I21" s="27" t="s">
+      <c r="M21" s="2"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A22" s="33"/>
+      <c r="B22" s="33"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="M22" s="2"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E23" s="43"/>
+      <c r="F23" s="43"/>
+      <c r="I23" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="M21" s="2"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="26"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
+      <c r="J23" s="54"/>
+      <c r="K23" s="54"/>
+      <c r="M23" s="2"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="26"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="E26" s="43"/>
+      <c r="F26" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="J3:L3"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="J5:L5"/>
-    <mergeCell ref="E20:F20"/>
+  <mergeCells count="36">
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="E22:F22"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
@@ -1521,16 +1634,24 @@
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
     <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="E19:F19"/>
-    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="J5:L5"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="J3:L3"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{A8D390F2-6B07-4EFD-A705-61078C4CD09A}"/>
